--- a/segreteria/Calendario esami LM.xlsx
+++ b/segreteria/Calendario esami LM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saint\unipavia\segreteria\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{380983EA-90B0-4596-9B68-73D0919A5128}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73A6277E-F146-4E4B-AA75-B5C7152BAD30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D2E6C525-4344-462D-A48F-BF1A80500AB8}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{D2E6C525-4344-462D-A48F-BF1A80500AB8}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -618,7 +618,16 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{391D1BE4-0BCF-4ED4-8F72-2B4D7E4679F8}" name="Tabella1" displayName="Tabella1" ref="A1:F55" totalsRowShown="0" headerRowDxfId="10" dataDxfId="8" headerRowBorderDxfId="9" tableBorderDxfId="7" totalsRowBorderDxfId="6">
-  <autoFilter ref="A1:F55" xr:uid="{391D1BE4-0BCF-4ED4-8F72-2B4D7E4679F8}"/>
+  <autoFilter ref="A1:F55" xr:uid="{391D1BE4-0BCF-4ED4-8F72-2B4D7E4679F8}">
+    <filterColumn colId="5">
+      <filters>
+        <filter val="1^sem"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F55">
+    <sortCondition ref="C1:C55"/>
+  </sortState>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{E177C9D9-7AD9-4155-A2AD-1B93B3868407}" name="InsegnamentoCourse" dataDxfId="5"/>
     <tableColumn id="2" xr3:uid="{D087D171-9B99-4020-9B8D-EF32EAAFD762}" name="DocenteTeacher" dataDxfId="4"/>
@@ -1000,81 +1009,81 @@
         <v>44</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="C3" s="7">
-        <v>46071</v>
+        <v>46042</v>
       </c>
       <c r="D3" s="8">
         <v>0.58333333333333337</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="C4" s="7">
-        <v>46195</v>
+        <v>46043</v>
       </c>
       <c r="D4" s="8">
-        <v>0.58333333333333337</v>
+        <v>0.39583333333333331</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F4" s="9" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="C5" s="7">
-        <v>46212</v>
+        <v>46043</v>
       </c>
       <c r="D5" s="8">
-        <v>0.58333333333333337</v>
+        <v>0.39583333333333331</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="C6" s="7">
-        <v>46273</v>
+        <v>46045</v>
       </c>
       <c r="D6" s="8">
-        <v>0.58333333333333337</v>
+        <v>0.39583333333333331</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="F6" s="9" t="s">
         <v>44</v>
@@ -1082,179 +1091,179 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C7" s="7">
-        <v>46286</v>
+        <v>46048</v>
       </c>
       <c r="D7" s="8">
         <v>0.58333333333333337</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F7" s="9" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="C8" s="7">
-        <v>46048</v>
+        <v>46050</v>
       </c>
       <c r="D8" s="8">
-        <v>0.58333333333333337</v>
+        <v>0.60416666666666663</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="C9" s="7">
-        <v>46072</v>
+        <v>46050</v>
       </c>
       <c r="D9" s="8">
-        <v>0.58333333333333337</v>
+        <v>0.60416666666666663</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="C10" s="7">
-        <v>46197</v>
+        <v>46055</v>
       </c>
       <c r="D10" s="8">
         <v>0.375</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="C11" s="7">
-        <v>46231</v>
+        <v>46062</v>
       </c>
       <c r="D11" s="8">
-        <v>0.58333333333333337</v>
+        <v>0.375</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="7">
+        <v>46070</v>
+      </c>
+      <c r="D12" s="8">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" s="7">
+        <v>46070</v>
+      </c>
+      <c r="D13" s="8">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C14" s="7">
+        <v>46071</v>
+      </c>
+      <c r="D14" s="8">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="7">
-        <v>46267</v>
-      </c>
-      <c r="D12" s="8">
+      <c r="C15" s="7">
+        <v>46072</v>
+      </c>
+      <c r="D15" s="8">
         <v>0.58333333333333337</v>
       </c>
-      <c r="E12" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="F12" s="9" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="7">
-        <v>46287</v>
-      </c>
-      <c r="D13" s="8">
-        <v>0.58333333333333337</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F13" s="9" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C14" s="7">
-        <v>46045</v>
-      </c>
-      <c r="D14" s="8">
-        <v>0.39583333333333331</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F14" s="9" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C15" s="7">
-        <v>46076</v>
-      </c>
-      <c r="D15" s="8">
-        <v>0.39583333333333331</v>
-      </c>
       <c r="E15" s="6" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="F15" s="9" t="s">
         <v>44</v>
@@ -1268,136 +1277,136 @@
         <v>14</v>
       </c>
       <c r="C16" s="7">
-        <v>46189</v>
+        <v>46076</v>
       </c>
       <c r="D16" s="8">
         <v>0.39583333333333331</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F16" s="9" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="C17" s="7">
-        <v>46209</v>
+        <v>46079</v>
       </c>
       <c r="D17" s="8">
-        <v>0.39583333333333331</v>
+        <v>0.60416666666666663</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="C18" s="7">
-        <v>46272</v>
+        <v>46079</v>
       </c>
       <c r="D18" s="8">
-        <v>0.39583333333333331</v>
+        <v>0.60416666666666663</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>17</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C19" s="7">
+        <v>46080</v>
+      </c>
+      <c r="D19" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C20" s="7">
+        <v>46188</v>
+      </c>
+      <c r="D20" s="8">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A21" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B21" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C19" s="7">
-        <v>46288</v>
-      </c>
-      <c r="D19" s="8">
-        <v>0.39583333333333331</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F19" s="9" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C20" s="7">
-        <v>46043</v>
-      </c>
-      <c r="D20" s="8">
-        <v>0.39583333333333331</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="F20" s="9" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>20</v>
-      </c>
       <c r="C21" s="7">
-        <v>46070</v>
+        <v>46189</v>
       </c>
       <c r="D21" s="8">
         <v>0.39583333333333331</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="C22" s="7">
-        <v>46191</v>
+        <v>46190</v>
       </c>
       <c r="D22" s="8">
-        <v>0.39583333333333331</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -1408,7 +1417,7 @@
         <v>20</v>
       </c>
       <c r="C23" s="7">
-        <v>46227</v>
+        <v>46191</v>
       </c>
       <c r="D23" s="8">
         <v>0.39583333333333331</v>
@@ -1420,41 +1429,41 @@
         <v>44</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>20</v>
       </c>
       <c r="C24" s="7">
-        <v>46273</v>
+        <v>46191</v>
       </c>
       <c r="D24" s="8">
         <v>0.39583333333333331</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="C25" s="7">
-        <v>46288</v>
+        <v>46195</v>
       </c>
       <c r="D25" s="8">
-        <v>0.39583333333333331</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>44</v>
@@ -1462,125 +1471,125 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C26" s="7">
-        <v>46043</v>
+        <v>46197</v>
       </c>
       <c r="D26" s="8">
-        <v>0.39583333333333331</v>
+        <v>0.375</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C27" s="7">
-        <v>46070</v>
+        <v>46206</v>
       </c>
       <c r="D27" s="8">
-        <v>0.39583333333333331</v>
+        <v>0.60416666666666663</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="C28" s="7">
-        <v>46191</v>
+        <v>46206</v>
       </c>
       <c r="D28" s="8">
-        <v>0.39583333333333331</v>
+        <v>0.60416666666666663</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F28" s="9" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C29" s="7">
-        <v>46227</v>
+        <v>46209</v>
       </c>
       <c r="D29" s="8">
         <v>0.39583333333333331</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="C30" s="7">
-        <v>46273</v>
+        <v>46212</v>
       </c>
       <c r="D30" s="8">
-        <v>0.39583333333333331</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="C31" s="7">
-        <v>46288</v>
+        <v>46213</v>
       </c>
       <c r="D31" s="8">
-        <v>0.39583333333333331</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
         <v>29</v>
       </c>
@@ -1588,7 +1597,7 @@
         <v>26</v>
       </c>
       <c r="C32" s="7">
-        <v>46050</v>
+        <v>46224</v>
       </c>
       <c r="D32" s="8">
         <v>0.60416666666666663</v>
@@ -1600,121 +1609,121 @@
         <v>45</v>
       </c>
     </row>
-    <row r="33" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C33" s="7">
-        <v>46079</v>
+        <v>46224</v>
       </c>
       <c r="D33" s="8">
         <v>0.60416666666666663</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="34" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="C34" s="7">
-        <v>46206</v>
+        <v>46226</v>
       </c>
       <c r="D34" s="8">
-        <v>0.60416666666666663</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="F34" s="9" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="35" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C35" s="7">
-        <v>46224</v>
+        <v>46227</v>
       </c>
       <c r="D35" s="8">
-        <v>0.60416666666666663</v>
+        <v>0.39583333333333331</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C36" s="7">
-        <v>46274</v>
+        <v>46227</v>
       </c>
       <c r="D36" s="8">
-        <v>0.60416666666666663</v>
+        <v>0.39583333333333331</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F36" s="9" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="37" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="C37" s="7">
-        <v>46288</v>
+        <v>46231</v>
       </c>
       <c r="D37" s="8">
-        <v>0.60416666666666663</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="E37" s="6" t="s">
         <v>12</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C38" s="7">
-        <v>46050</v>
+        <v>46265</v>
       </c>
       <c r="D38" s="8">
-        <v>0.60416666666666663</v>
+        <v>0.375</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="F38" s="9" t="s">
         <v>45</v>
@@ -1722,165 +1731,165 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="C39" s="7">
-        <v>46079</v>
+        <v>46267</v>
       </c>
       <c r="D39" s="8">
-        <v>0.60416666666666663</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="E39" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="F39" s="9" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C40" s="7">
+        <v>46268</v>
+      </c>
+      <c r="D40" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="F40" s="9" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A41" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C41" s="7">
+        <v>46272</v>
+      </c>
+      <c r="D41" s="8">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="E41" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="F39" s="9" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C40" s="7">
-        <v>46206</v>
-      </c>
-      <c r="D40" s="8">
-        <v>0.60416666666666663</v>
-      </c>
-      <c r="E40" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="F40" s="9" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C41" s="7">
-        <v>46224</v>
-      </c>
-      <c r="D41" s="8">
-        <v>0.60416666666666663</v>
-      </c>
-      <c r="E41" s="6" t="s">
-        <v>27</v>
-      </c>
       <c r="F41" s="9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="C42" s="7">
-        <v>46274</v>
+        <v>46273</v>
       </c>
       <c r="D42" s="8">
-        <v>0.60416666666666663</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F42" s="9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C43" s="7">
+        <v>46273</v>
+      </c>
+      <c r="D43" s="8">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="E43" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F43" s="9" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C44" s="7">
+        <v>46273</v>
+      </c>
+      <c r="D44" s="8">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="E44" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F44" s="9" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C45" s="7">
+        <v>46274</v>
+      </c>
+      <c r="D45" s="8">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="E45" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F45" s="9" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B43" s="6" t="s">
+      <c r="B46" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C43" s="7">
-        <v>46288</v>
-      </c>
-      <c r="D43" s="8">
+      <c r="C46" s="7">
+        <v>46274</v>
+      </c>
+      <c r="D46" s="8">
         <v>0.60416666666666663</v>
       </c>
-      <c r="E43" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F43" s="9" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="C44" s="7">
-        <v>46055</v>
-      </c>
-      <c r="D44" s="8">
-        <v>0.375</v>
-      </c>
-      <c r="E44" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="F44" s="9" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="C45" s="7">
-        <v>46080</v>
-      </c>
-      <c r="D45" s="8">
-        <v>0.375</v>
-      </c>
-      <c r="E45" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F45" s="9" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="C46" s="7">
-        <v>46190</v>
-      </c>
-      <c r="D46" s="8">
-        <v>0.58333333333333337</v>
-      </c>
       <c r="E46" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F46" s="9" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
         <v>32</v>
       </c>
@@ -1888,33 +1897,33 @@
         <v>33</v>
       </c>
       <c r="C47" s="7">
-        <v>46213</v>
+        <v>46280</v>
       </c>
       <c r="D47" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="E47" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F47" s="9" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C48" s="7">
+        <v>46282</v>
+      </c>
+      <c r="D48" s="8">
         <v>0.58333333333333337</v>
       </c>
-      <c r="E47" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="F47" s="9" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="C48" s="7">
-        <v>46265</v>
-      </c>
-      <c r="D48" s="8">
-        <v>0.375</v>
-      </c>
       <c r="E48" s="6" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="F48" s="9" t="s">
         <v>45</v>
@@ -1922,33 +1931,33 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="C49" s="7">
-        <v>46280</v>
+        <v>46286</v>
       </c>
       <c r="D49" s="8">
-        <v>0.375</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="F49" s="9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="C50" s="7">
-        <v>46042</v>
+        <v>46287</v>
       </c>
       <c r="D50" s="8">
         <v>0.58333333333333337</v>
@@ -1957,104 +1966,104 @@
         <v>13</v>
       </c>
       <c r="F50" s="9" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="C51" s="7">
-        <v>46062</v>
+        <v>46288</v>
       </c>
       <c r="D51" s="8">
-        <v>0.375</v>
+        <v>0.39583333333333331</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F51" s="9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="C52" s="7">
-        <v>46188</v>
+        <v>46288</v>
       </c>
       <c r="D52" s="8">
-        <v>0.58333333333333337</v>
+        <v>0.39583333333333331</v>
       </c>
       <c r="E52" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="F52" s="9" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C53" s="7">
+        <v>46288</v>
+      </c>
+      <c r="D53" s="8">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="E53" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="F53" s="9" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C54" s="7">
+        <v>46288</v>
+      </c>
+      <c r="D54" s="8">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="E54" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F52" s="9" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="C53" s="7">
-        <v>46226</v>
-      </c>
-      <c r="D53" s="8">
-        <v>0.58333333333333337</v>
-      </c>
-      <c r="E53" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="F53" s="9" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="C54" s="7">
-        <v>46268</v>
-      </c>
-      <c r="D54" s="8">
-        <v>0.375</v>
-      </c>
-      <c r="E54" s="6" t="s">
-        <v>34</v>
-      </c>
       <c r="F54" s="9" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="10" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B55" s="11" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="C55" s="12">
-        <v>46282</v>
+        <v>46288</v>
       </c>
       <c r="D55" s="13">
-        <v>0.58333333333333337</v>
+        <v>0.60416666666666663</v>
       </c>
       <c r="E55" s="11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>45</v>

--- a/segreteria/Calendario esami LM.xlsx
+++ b/segreteria/Calendario esami LM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saint\unipavia\segreteria\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73A6277E-F146-4E4B-AA75-B5C7152BAD30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C404D518-2E69-4DC9-BDFD-E76AB847E414}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{D2E6C525-4344-462D-A48F-BF1A80500AB8}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D2E6C525-4344-462D-A48F-BF1A80500AB8}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="48">
   <si>
     <t xml:space="preserve">Foundations of cybersecurity </t>
   </si>
@@ -174,6 +174,12 @@
   </si>
   <si>
     <t>2^sem</t>
+  </si>
+  <si>
+    <t>Posizione</t>
+  </si>
+  <si>
+    <t>==</t>
   </si>
 </sst>
 </file>
@@ -315,7 +321,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -356,11 +362,17 @@
     <xf numFmtId="20" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="11">
+  <dxfs count="12">
+    <dxf>
+      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
@@ -617,24 +629,19 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{391D1BE4-0BCF-4ED4-8F72-2B4D7E4679F8}" name="Tabella1" displayName="Tabella1" ref="A1:F55" totalsRowShown="0" headerRowDxfId="10" dataDxfId="8" headerRowBorderDxfId="9" tableBorderDxfId="7" totalsRowBorderDxfId="6">
-  <autoFilter ref="A1:F55" xr:uid="{391D1BE4-0BCF-4ED4-8F72-2B4D7E4679F8}">
-    <filterColumn colId="5">
-      <filters>
-        <filter val="1^sem"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{391D1BE4-0BCF-4ED4-8F72-2B4D7E4679F8}" name="Tabella1" displayName="Tabella1" ref="A1:G55" totalsRowShown="0" headerRowDxfId="11" dataDxfId="9" headerRowBorderDxfId="10" tableBorderDxfId="8" totalsRowBorderDxfId="7">
+  <autoFilter ref="A1:G55" xr:uid="{391D1BE4-0BCF-4ED4-8F72-2B4D7E4679F8}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F55">
     <sortCondition ref="C1:C55"/>
   </sortState>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{E177C9D9-7AD9-4155-A2AD-1B93B3868407}" name="InsegnamentoCourse" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{D087D171-9B99-4020-9B8D-EF32EAAFD762}" name="DocenteTeacher" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{67F91E60-E998-44B0-A271-48776D83610B}" name="DataDate" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{12C993FC-584A-41C1-BB64-7A32077C4B47}" name="OraHour" dataDxfId="2"/>
-    <tableColumn id="5" xr3:uid="{61F4A729-F5DC-41B5-B1F5-6920A2660C0B}" name="AulaRoom" dataDxfId="1"/>
-    <tableColumn id="6" xr3:uid="{6035D1EE-EC18-461E-A4D8-5CE5DFEAAE58}" name="NotaNote" dataDxfId="0"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{E177C9D9-7AD9-4155-A2AD-1B93B3868407}" name="InsegnamentoCourse" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{D087D171-9B99-4020-9B8D-EF32EAAFD762}" name="DocenteTeacher" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{67F91E60-E998-44B0-A271-48776D83610B}" name="DataDate" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{12C993FC-584A-41C1-BB64-7A32077C4B47}" name="OraHour" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{61F4A729-F5DC-41B5-B1F5-6920A2660C0B}" name="AulaRoom" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{6035D1EE-EC18-461E-A4D8-5CE5DFEAAE58}" name="NotaNote" dataDxfId="1"/>
+    <tableColumn id="7" xr3:uid="{112C0ECD-4A48-44DC-85C7-F47983378192}" name="Posizione" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium17" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -957,7 +964,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44D4FA9C-9214-46C7-BAC6-5AFA7DE75702}">
-  <dimension ref="A1:F55"/>
+  <dimension ref="A1:G55"/>
   <sheetFormatPr defaultColWidth="39.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="34.5703125" style="4" bestFit="1" customWidth="1"/>
@@ -965,11 +972,11 @@
     <col min="3" max="3" width="13.7109375" style="4" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13" style="4" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.7109375" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.28515625" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="39.42578125" style="4"/>
+    <col min="6" max="7" width="14.28515625" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="39.42578125" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>38</v>
       </c>
@@ -988,8 +995,11 @@
       <c r="F1" s="3" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>0</v>
       </c>
@@ -1008,8 +1018,11 @@
       <c r="F2" s="9" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G2" s="14" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>35</v>
       </c>
@@ -1028,8 +1041,11 @@
       <c r="F3" s="9" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G3" s="14" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>19</v>
       </c>
@@ -1048,8 +1064,11 @@
       <c r="F4" s="9" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G4" s="14" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>25</v>
       </c>
@@ -1068,8 +1087,11 @@
       <c r="F5" s="9" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="G5" s="14" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>18</v>
       </c>
@@ -1088,8 +1110,11 @@
       <c r="F6" s="9" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G6" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>8</v>
       </c>
@@ -1108,8 +1133,11 @@
       <c r="F7" s="9" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G7" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>29</v>
       </c>
@@ -1128,8 +1156,11 @@
       <c r="F8" s="9" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G8" s="14" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>30</v>
       </c>
@@ -1148,8 +1179,11 @@
       <c r="F9" s="9" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G9" s="14" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>32</v>
       </c>
@@ -1168,8 +1202,11 @@
       <c r="F10" s="9" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G10" s="14" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>35</v>
       </c>
@@ -1188,8 +1225,11 @@
       <c r="F11" s="9" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G11" s="14" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>19</v>
       </c>
@@ -1208,8 +1248,11 @@
       <c r="F12" s="9" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G12" s="9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>25</v>
       </c>
@@ -1228,8 +1271,11 @@
       <c r="F13" s="9" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G13" s="14" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>0</v>
       </c>
@@ -1248,8 +1294,9 @@
       <c r="F14" s="9" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G14" s="9"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>8</v>
       </c>
@@ -1268,8 +1315,11 @@
       <c r="F15" s="9" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="G15" s="14" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>18</v>
       </c>
@@ -1288,8 +1338,11 @@
       <c r="F16" s="9" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G16" s="14" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>29</v>
       </c>
@@ -1308,8 +1361,11 @@
       <c r="F17" s="9" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G17" s="14" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
         <v>30</v>
       </c>
@@ -1328,8 +1384,11 @@
       <c r="F18" s="9" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G18" s="14" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
         <v>32</v>
       </c>
@@ -1348,8 +1407,11 @@
       <c r="F19" s="9" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G19" s="14" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
         <v>35</v>
       </c>
@@ -1368,8 +1430,11 @@
       <c r="F20" s="9" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="G20" s="9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>18</v>
       </c>
@@ -1388,8 +1453,11 @@
       <c r="F21" s="9" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G21" s="14" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
         <v>32</v>
       </c>
@@ -1408,8 +1476,9 @@
       <c r="F22" s="9" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G22" s="9"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
         <v>19</v>
       </c>
@@ -1428,8 +1497,11 @@
       <c r="F23" s="9" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G23" s="14" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
         <v>25</v>
       </c>
@@ -1448,8 +1520,9 @@
       <c r="F24" s="9" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G24" s="9"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
         <v>0</v>
       </c>
@@ -1468,8 +1541,9 @@
       <c r="F25" s="9" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G25" s="9"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
         <v>8</v>
       </c>
@@ -1488,8 +1562,11 @@
       <c r="F26" s="9" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="27" spans="1:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G26" s="14" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
         <v>29</v>
       </c>
@@ -1508,8 +1585,11 @@
       <c r="F27" s="9" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="28" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G27" s="14" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
         <v>30</v>
       </c>
@@ -1528,8 +1608,11 @@
       <c r="F28" s="9" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="29" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="G28" s="14" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
         <v>18</v>
       </c>
@@ -1548,8 +1631,11 @@
       <c r="F29" s="9" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G29" s="14" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
         <v>0</v>
       </c>
@@ -1568,8 +1654,11 @@
       <c r="F30" s="9" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="31" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G30" s="14" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
         <v>32</v>
       </c>
@@ -1588,8 +1677,11 @@
       <c r="F31" s="9" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="32" spans="1:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G31" s="14" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
         <v>29</v>
       </c>
@@ -1608,8 +1700,9 @@
       <c r="F32" s="9" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="33" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G32" s="9"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
         <v>30</v>
       </c>
@@ -1628,8 +1721,9 @@
       <c r="F33" s="9" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="34" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G33" s="9"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
         <v>35</v>
       </c>
@@ -1648,8 +1742,9 @@
       <c r="F34" s="9" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G34" s="9"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
         <v>19</v>
       </c>
@@ -1668,8 +1763,9 @@
       <c r="F35" s="9" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="36" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G35" s="9"/>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
         <v>25</v>
       </c>
@@ -1688,8 +1784,9 @@
       <c r="F36" s="9" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G36" s="9"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
         <v>8</v>
       </c>
@@ -1708,8 +1805,11 @@
       <c r="F37" s="9" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="38" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G37" s="14" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
         <v>32</v>
       </c>
@@ -1728,8 +1828,9 @@
       <c r="F38" s="9" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G38" s="9"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
         <v>8</v>
       </c>
@@ -1748,8 +1849,11 @@
       <c r="F39" s="9" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="40" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G39" s="14" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
         <v>35</v>
       </c>
@@ -1768,8 +1872,9 @@
       <c r="F40" s="9" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="41" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="G40" s="9"/>
+    </row>
+    <row r="41" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
         <v>18</v>
       </c>
@@ -1788,8 +1893,11 @@
       <c r="F41" s="9" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G41" s="14" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
         <v>0</v>
       </c>
@@ -1808,8 +1916,9 @@
       <c r="F42" s="9" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G42" s="9"/>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
         <v>19</v>
       </c>
@@ -1828,8 +1937,11 @@
       <c r="F43" s="9" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="44" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G43" s="14" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
         <v>25</v>
       </c>
@@ -1848,8 +1960,11 @@
       <c r="F44" s="9" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="45" spans="1:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G44" s="9">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
         <v>29</v>
       </c>
@@ -1868,8 +1983,11 @@
       <c r="F45" s="9" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="46" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G45" s="9">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
         <v>30</v>
       </c>
@@ -1888,8 +2006,9 @@
       <c r="F46" s="9" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="47" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G46" s="9"/>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
         <v>32</v>
       </c>
@@ -1908,8 +2027,9 @@
       <c r="F47" s="9" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="48" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G47" s="9"/>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
         <v>35</v>
       </c>
@@ -1928,8 +2048,9 @@
       <c r="F48" s="9" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G48" s="9"/>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
         <v>0</v>
       </c>
@@ -1948,8 +2069,9 @@
       <c r="F49" s="9" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G49" s="9"/>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
         <v>8</v>
       </c>
@@ -1968,8 +2090,11 @@
       <c r="F50" s="9" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="51" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="G50" s="14" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
         <v>18</v>
       </c>
@@ -1988,8 +2113,11 @@
       <c r="F51" s="9" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G51" s="14" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
         <v>19</v>
       </c>
@@ -2008,8 +2136,11 @@
       <c r="F52" s="9" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="53" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G52" s="14" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
         <v>25</v>
       </c>
@@ -2028,8 +2159,9 @@
       <c r="F53" s="9" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="54" spans="1:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G53" s="9"/>
+    </row>
+    <row r="54" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
         <v>29</v>
       </c>
@@ -2048,8 +2180,9 @@
       <c r="F54" s="9" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="55" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G54" s="9"/>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="10" t="s">
         <v>30</v>
       </c>
@@ -2068,6 +2201,7 @@
       <c r="F55" s="9" t="s">
         <v>45</v>
       </c>
+      <c r="G55" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/segreteria/Calendario esami LM.xlsx
+++ b/segreteria/Calendario esami LM.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saint\unipavia\segreteria\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C404D518-2E69-4DC9-BDFD-E76AB847E414}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F63D43B4-2E15-434C-9E7E-F98238FC1CA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D2E6C525-4344-462D-A48F-BF1A80500AB8}"/>
   </bookViews>
@@ -186,7 +186,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -199,6 +199,21 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -321,7 +336,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -365,6 +380,24 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -630,7 +663,13 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{391D1BE4-0BCF-4ED4-8F72-2B4D7E4679F8}" name="Tabella1" displayName="Tabella1" ref="A1:G55" totalsRowShown="0" headerRowDxfId="11" dataDxfId="9" headerRowBorderDxfId="10" tableBorderDxfId="8" totalsRowBorderDxfId="7">
-  <autoFilter ref="A1:G55" xr:uid="{391D1BE4-0BCF-4ED4-8F72-2B4D7E4679F8}"/>
+  <autoFilter ref="A1:G55" xr:uid="{391D1BE4-0BCF-4ED4-8F72-2B4D7E4679F8}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="Numerical methods in engineering sciences"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F55">
     <sortCondition ref="C1:C55"/>
   </sortState>
@@ -999,7 +1038,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>0</v>
       </c>
@@ -1022,7 +1061,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>35</v>
       </c>
@@ -1045,7 +1084,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>19</v>
       </c>
@@ -1068,7 +1107,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>25</v>
       </c>
@@ -1114,7 +1153,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>8</v>
       </c>
@@ -1137,7 +1176,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>29</v>
       </c>
@@ -1160,7 +1199,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>30</v>
       </c>
@@ -1183,7 +1222,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>32</v>
       </c>
@@ -1206,7 +1245,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>35</v>
       </c>
@@ -1229,7 +1268,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>19</v>
       </c>
@@ -1252,7 +1291,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>25</v>
       </c>
@@ -1275,7 +1314,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>0</v>
       </c>
@@ -1296,7 +1335,7 @@
       </c>
       <c r="G14" s="9"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>8</v>
       </c>
@@ -1320,29 +1359,29 @@
       </c>
     </row>
     <row r="16" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="C16" s="7">
+      <c r="C16" s="17">
         <v>46076</v>
       </c>
-      <c r="D16" s="8">
+      <c r="D16" s="18">
         <v>0.39583333333333331</v>
       </c>
-      <c r="E16" s="6" t="s">
+      <c r="E16" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="F16" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="G16" s="14" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="F16" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="G16" s="20" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>29</v>
       </c>
@@ -1365,7 +1404,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
         <v>30</v>
       </c>
@@ -1388,7 +1427,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
         <v>32</v>
       </c>
@@ -1411,7 +1450,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
         <v>35</v>
       </c>
@@ -1435,29 +1474,29 @@
       </c>
     </row>
     <row r="21" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="C21" s="7">
+      <c r="C21" s="17">
         <v>46189</v>
       </c>
-      <c r="D21" s="8">
+      <c r="D21" s="18">
         <v>0.39583333333333331</v>
       </c>
-      <c r="E21" s="6" t="s">
+      <c r="E21" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="F21" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="G21" s="14" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F21" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="G21" s="20" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
         <v>32</v>
       </c>
@@ -1478,7 +1517,7 @@
       </c>
       <c r="G22" s="9"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
         <v>19</v>
       </c>
@@ -1501,7 +1540,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
         <v>25</v>
       </c>
@@ -1522,7 +1561,7 @@
       </c>
       <c r="G24" s="9"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
         <v>0</v>
       </c>
@@ -1543,7 +1582,7 @@
       </c>
       <c r="G25" s="9"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
         <v>8</v>
       </c>
@@ -1566,7 +1605,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
         <v>29</v>
       </c>
@@ -1589,7 +1628,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
         <v>30</v>
       </c>
@@ -1613,29 +1652,29 @@
       </c>
     </row>
     <row r="29" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A29" s="5" t="s">
+      <c r="A29" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="B29" s="6" t="s">
+      <c r="B29" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="C29" s="7">
+      <c r="C29" s="17">
         <v>46209</v>
       </c>
-      <c r="D29" s="8">
+      <c r="D29" s="18">
         <v>0.39583333333333331</v>
       </c>
-      <c r="E29" s="6" t="s">
+      <c r="E29" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="F29" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="G29" s="14" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F29" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="G29" s="20" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
         <v>0</v>
       </c>
@@ -1658,7 +1697,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
         <v>32</v>
       </c>
@@ -1681,7 +1720,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
         <v>29</v>
       </c>
@@ -1702,7 +1741,7 @@
       </c>
       <c r="G32" s="9"/>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
         <v>30</v>
       </c>
@@ -1723,7 +1762,7 @@
       </c>
       <c r="G33" s="9"/>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
         <v>35</v>
       </c>
@@ -1744,7 +1783,7 @@
       </c>
       <c r="G34" s="9"/>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
         <v>19</v>
       </c>
@@ -1765,7 +1804,7 @@
       </c>
       <c r="G35" s="9"/>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
         <v>25</v>
       </c>
@@ -1786,7 +1825,7 @@
       </c>
       <c r="G36" s="9"/>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
         <v>8</v>
       </c>
@@ -1809,7 +1848,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
         <v>32</v>
       </c>
@@ -1830,7 +1869,7 @@
       </c>
       <c r="G38" s="9"/>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
         <v>8</v>
       </c>
@@ -1853,7 +1892,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
         <v>35</v>
       </c>
@@ -1875,29 +1914,29 @@
       <c r="G40" s="9"/>
     </row>
     <row r="41" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A41" s="5" t="s">
+      <c r="A41" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="B41" s="6" t="s">
+      <c r="B41" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="C41" s="7">
+      <c r="C41" s="17">
         <v>46272</v>
       </c>
-      <c r="D41" s="8">
+      <c r="D41" s="18">
         <v>0.39583333333333331</v>
       </c>
-      <c r="E41" s="6" t="s">
+      <c r="E41" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="F41" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="G41" s="14" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F41" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="G41" s="20" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
         <v>0</v>
       </c>
@@ -1918,7 +1957,7 @@
       </c>
       <c r="G42" s="9"/>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
         <v>19</v>
       </c>
@@ -1941,7 +1980,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
         <v>25</v>
       </c>
@@ -1964,7 +2003,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
         <v>29</v>
       </c>
@@ -1987,7 +2026,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
         <v>30</v>
       </c>
@@ -2008,7 +2047,7 @@
       </c>
       <c r="G46" s="9"/>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
         <v>32</v>
       </c>
@@ -2029,7 +2068,7 @@
       </c>
       <c r="G47" s="9"/>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
         <v>35</v>
       </c>
@@ -2050,7 +2089,7 @@
       </c>
       <c r="G48" s="9"/>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
         <v>0</v>
       </c>
@@ -2071,7 +2110,7 @@
       </c>
       <c r="G49" s="9"/>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
         <v>8</v>
       </c>
@@ -2095,29 +2134,29 @@
       </c>
     </row>
     <row r="51" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A51" s="5" t="s">
+      <c r="A51" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="B51" s="6" t="s">
+      <c r="B51" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="C51" s="7">
+      <c r="C51" s="17">
         <v>46288</v>
       </c>
-      <c r="D51" s="8">
+      <c r="D51" s="18">
         <v>0.39583333333333331</v>
       </c>
-      <c r="E51" s="6" t="s">
+      <c r="E51" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="F51" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="G51" s="14" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F51" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="G51" s="20" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
         <v>19</v>
       </c>
@@ -2140,7 +2179,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
         <v>25</v>
       </c>
@@ -2161,7 +2200,7 @@
       </c>
       <c r="G53" s="9"/>
     </row>
-    <row r="54" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
         <v>29</v>
       </c>
@@ -2182,7 +2221,7 @@
       </c>
       <c r="G54" s="9"/>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="10" t="s">
         <v>30</v>
       </c>

--- a/segreteria/Calendario esami LM.xlsx
+++ b/segreteria/Calendario esami LM.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saint\unipavia\segreteria\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F63D43B4-2E15-434C-9E7E-F98238FC1CA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AD82ACF-FA57-4BCA-892D-7398FC744163}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D2E6C525-4344-462D-A48F-BF1A80500AB8}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="48">
   <si>
     <t xml:space="preserve">Foundations of cybersecurity </t>
   </si>
@@ -663,13 +663,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{391D1BE4-0BCF-4ED4-8F72-2B4D7E4679F8}" name="Tabella1" displayName="Tabella1" ref="A1:G55" totalsRowShown="0" headerRowDxfId="11" dataDxfId="9" headerRowBorderDxfId="10" tableBorderDxfId="8" totalsRowBorderDxfId="7">
-  <autoFilter ref="A1:G55" xr:uid="{391D1BE4-0BCF-4ED4-8F72-2B4D7E4679F8}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="Numerical methods in engineering sciences"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:G55" xr:uid="{391D1BE4-0BCF-4ED4-8F72-2B4D7E4679F8}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F55">
     <sortCondition ref="C1:C55"/>
   </sortState>
@@ -1038,7 +1032,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="2" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>0</v>
       </c>
@@ -1061,7 +1055,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>35</v>
       </c>
@@ -1084,7 +1078,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="4" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>19</v>
       </c>
@@ -1107,7 +1101,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="5" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>25</v>
       </c>
@@ -1153,7 +1147,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>8</v>
       </c>
@@ -1176,7 +1170,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>29</v>
       </c>
@@ -1199,7 +1193,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="9" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>30</v>
       </c>
@@ -1222,7 +1216,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="10" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>32</v>
       </c>
@@ -1245,7 +1239,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="11" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>35</v>
       </c>
@@ -1268,7 +1262,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="12" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>19</v>
       </c>
@@ -1287,11 +1281,11 @@
       <c r="F12" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G12" s="9">
+      <c r="G12" s="19">
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>25</v>
       </c>
@@ -1314,7 +1308,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="14" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>0</v>
       </c>
@@ -1335,7 +1329,7 @@
       </c>
       <c r="G14" s="9"/>
     </row>
-    <row r="15" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>8</v>
       </c>
@@ -1381,7 +1375,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>29</v>
       </c>
@@ -1404,7 +1398,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
         <v>30</v>
       </c>
@@ -1427,7 +1421,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
         <v>32</v>
       </c>
@@ -1450,7 +1444,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="20" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
         <v>35</v>
       </c>
@@ -1470,7 +1464,7 @@
         <v>45</v>
       </c>
       <c r="G20" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="30" x14ac:dyDescent="0.25">
@@ -1496,7 +1490,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="22" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
         <v>32</v>
       </c>
@@ -1515,9 +1509,11 @@
       <c r="F22" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="G22" s="9"/>
-    </row>
-    <row r="23" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G22" s="9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
         <v>19</v>
       </c>
@@ -1536,11 +1532,11 @@
       <c r="F23" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G23" s="14" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G23" s="14">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
         <v>25</v>
       </c>
@@ -1559,9 +1555,11 @@
       <c r="F24" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="G24" s="9"/>
-    </row>
-    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G24" s="9">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
         <v>0</v>
       </c>
@@ -1580,9 +1578,11 @@
       <c r="F25" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G25" s="9"/>
-    </row>
-    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G25" s="9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
         <v>8</v>
       </c>
@@ -1605,7 +1605,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
         <v>29</v>
       </c>
@@ -1628,7 +1628,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
         <v>30</v>
       </c>
@@ -1674,7 +1674,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
         <v>0</v>
       </c>
@@ -1697,7 +1697,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
         <v>32</v>
       </c>
@@ -1720,7 +1720,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
         <v>29</v>
       </c>
@@ -1739,9 +1739,11 @@
       <c r="F32" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="G32" s="9"/>
-    </row>
-    <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G32" s="9">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
         <v>30</v>
       </c>
@@ -1760,9 +1762,11 @@
       <c r="F33" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="G33" s="9"/>
-    </row>
-    <row r="34" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="G33" s="9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
         <v>35</v>
       </c>
@@ -1783,7 +1787,7 @@
       </c>
       <c r="G34" s="9"/>
     </row>
-    <row r="35" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
         <v>19</v>
       </c>
@@ -1804,7 +1808,7 @@
       </c>
       <c r="G35" s="9"/>
     </row>
-    <row r="36" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
         <v>25</v>
       </c>
@@ -1825,7 +1829,7 @@
       </c>
       <c r="G36" s="9"/>
     </row>
-    <row r="37" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
         <v>8</v>
       </c>
@@ -1848,7 +1852,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="38" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
         <v>32</v>
       </c>
@@ -1869,7 +1873,7 @@
       </c>
       <c r="G38" s="9"/>
     </row>
-    <row r="39" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
         <v>8</v>
       </c>
@@ -1892,7 +1896,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="40" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
         <v>35</v>
       </c>
@@ -1936,7 +1940,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="42" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
         <v>0</v>
       </c>
@@ -1957,7 +1961,7 @@
       </c>
       <c r="G42" s="9"/>
     </row>
-    <row r="43" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
         <v>19</v>
       </c>
@@ -1980,7 +1984,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="44" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
         <v>25</v>
       </c>
@@ -2003,7 +2007,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
         <v>29</v>
       </c>
@@ -2026,7 +2030,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="46" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
         <v>30</v>
       </c>
@@ -2047,7 +2051,7 @@
       </c>
       <c r="G46" s="9"/>
     </row>
-    <row r="47" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
         <v>32</v>
       </c>
@@ -2068,7 +2072,7 @@
       </c>
       <c r="G47" s="9"/>
     </row>
-    <row r="48" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
         <v>35</v>
       </c>
@@ -2089,7 +2093,7 @@
       </c>
       <c r="G48" s="9"/>
     </row>
-    <row r="49" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
         <v>0</v>
       </c>
@@ -2110,7 +2114,7 @@
       </c>
       <c r="G49" s="9"/>
     </row>
-    <row r="50" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
         <v>8</v>
       </c>
@@ -2156,7 +2160,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="52" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
         <v>19</v>
       </c>
@@ -2179,7 +2183,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="53" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
         <v>25</v>
       </c>
@@ -2200,7 +2204,7 @@
       </c>
       <c r="G53" s="9"/>
     </row>
-    <row r="54" spans="1:7" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
         <v>29</v>
       </c>
@@ -2221,7 +2225,7 @@
       </c>
       <c r="G54" s="9"/>
     </row>
-    <row r="55" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="10" t="s">
         <v>30</v>
       </c>
@@ -2244,8 +2248,9 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
--- a/segreteria/Calendario esami LM.xlsx
+++ b/segreteria/Calendario esami LM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saint\unipavia\segreteria\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43796A4A-F715-47E2-B8DA-E7B6B8A7103A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F255CC6B-845B-44F9-9270-28A6B6A7D0B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,6 +17,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Table 1'!$A$1:$G$51</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Table 1'!$A$1:$G$50</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
@@ -1167,7 +1168,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
+  <sheetPr filterMode="1">
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:G51"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
@@ -1357,7 +1360,7 @@
       </c>
       <c r="G9" s="17"/>
     </row>
-    <row r="10" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" ht="15" hidden="1" x14ac:dyDescent="0.2">
       <c r="A10" s="9" t="s">
         <v>27</v>
       </c>
@@ -1374,9 +1377,7 @@
       <c r="F10" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="G10" s="10">
-        <v>5</v>
-      </c>
+      <c r="G10" s="10"/>
     </row>
     <row r="11" spans="1:7" ht="15" hidden="1" x14ac:dyDescent="0.2">
       <c r="A11" s="9" t="s">
@@ -1397,26 +1398,28 @@
       </c>
       <c r="G11" s="10"/>
     </row>
-    <row r="12" spans="1:7" ht="15" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="B12" s="10"/>
+    <row r="12" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A12" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B12" s="6"/>
       <c r="C12" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D12" s="12">
-        <v>46272</v>
-      </c>
-      <c r="E12" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="F12" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G12" s="10"/>
-    </row>
-    <row r="13" spans="1:7" ht="15" hidden="1" x14ac:dyDescent="0.2">
+        <v>36</v>
+      </c>
+      <c r="D12" s="7">
+        <v>46198</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G12" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A13" s="9" t="s">
         <v>27</v>
       </c>
@@ -1425,15 +1428,17 @@
         <v>28</v>
       </c>
       <c r="D13" s="12">
-        <v>46287</v>
+        <v>46272</v>
       </c>
       <c r="E13" s="13" t="s">
         <v>6</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="G13" s="10"/>
+        <v>20</v>
+      </c>
+      <c r="G13" s="10">
+        <v>7</v>
+      </c>
     </row>
     <row r="14" spans="1:7" s="21" customFormat="1" ht="14.25" hidden="1" x14ac:dyDescent="0.2">
       <c r="A14" s="22" t="s">
@@ -1492,25 +1497,25 @@
       </c>
       <c r="G16" s="6"/>
     </row>
-    <row r="17" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A17" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B17" s="6"/>
-      <c r="C17" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D17" s="7">
-        <v>46198</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F17" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G17" s="6">
-        <v>6</v>
+    <row r="17" spans="1:7" ht="30" x14ac:dyDescent="0.2">
+      <c r="A17" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B17" s="10"/>
+      <c r="C17" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D17" s="12">
+        <v>46274</v>
+      </c>
+      <c r="E17" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="F17" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="G17" s="10">
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="15" hidden="1" x14ac:dyDescent="0.2">
@@ -1532,25 +1537,25 @@
       </c>
       <c r="G18" s="6"/>
     </row>
-    <row r="19" spans="1:7" ht="30" x14ac:dyDescent="0.2">
-      <c r="A19" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="B19" s="10"/>
-      <c r="C19" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D19" s="12">
-        <v>46274</v>
-      </c>
-      <c r="E19" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="F19" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="G19" s="10">
-        <v>7</v>
+    <row r="19" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A19" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B19" s="6"/>
+      <c r="C19" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D19" s="7">
+        <v>46276</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G19" s="6">
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:7" s="21" customFormat="1" ht="14.25" hidden="1" x14ac:dyDescent="0.2">
@@ -1592,24 +1597,24 @@
       <c r="G21" s="23"/>
     </row>
     <row r="22" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A22" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="B22" s="6"/>
+      <c r="A22" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B22" s="10"/>
       <c r="C22" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D22" s="7">
-        <v>46276</v>
-      </c>
-      <c r="E22" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D22" s="12">
+        <v>46287</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="F22" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="G22" s="10">
         <v>9</v>
-      </c>
-      <c r="F22" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="G22" s="6">
-        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -2192,6 +2197,7 @@
       <sortCondition ref="G1:G51"/>
     </sortState>
   </autoFilter>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="77" fitToHeight="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
--- a/segreteria/Calendario esami LM.xlsx
+++ b/segreteria/Calendario esami LM.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saint\unipavia\segreteria\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saintgold\unipavia\segreteria\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F255CC6B-845B-44F9-9270-28A6B6A7D0B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94E225BA-0F7C-4271-BDD8-0EE6BDE07969}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="84">
   <si>
     <r>
       <rPr>
@@ -186,16 +186,6 @@
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
-      <t>E1</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="1"/>
-      </rPr>
       <t>E7</t>
     </r>
   </si>
@@ -245,45 +235,6 @@
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
-      <t>EF4</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">Leporati
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="1"/>
-      </rPr>
-      <t>Francesco,Torti Emanuele</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="1"/>
-      </rPr>
-      <t>EF1</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="1"/>
-      </rPr>
       <t>aula3</t>
     </r>
   </si>
@@ -335,26 +286,6 @@
         <family val="1"/>
       </rPr>
       <t>aula6</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="1"/>
-      </rPr>
-      <t>E3</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="1"/>
-      </rPr>
-      <t>E4</t>
     </r>
   </si>
   <si>
@@ -657,13 +588,52 @@
     <t>Ferie</t>
   </si>
   <si>
-    <t>2 - Ok - 18 - da conf</t>
-  </si>
-  <si>
     <t>1 - Ok - 24</t>
   </si>
   <si>
     <t>Forse</t>
+  </si>
+  <si>
+    <t>2 - Ok - 18</t>
+  </si>
+  <si>
+    <t>Iot mobile programming</t>
+  </si>
+  <si>
+    <t>Torti Emanuele</t>
+  </si>
+  <si>
+    <t>A2</t>
+  </si>
+  <si>
+    <t>A1</t>
+  </si>
+  <si>
+    <t>E3</t>
+  </si>
+  <si>
+    <t>Ok - 19 - manca proj</t>
+  </si>
+  <si>
+    <t>E4</t>
+  </si>
+  <si>
+    <t>Ok - 20</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="1"/>
+      </rPr>
+      <t>Leporati
+Francesco,Torti Emanuele</t>
+    </r>
+  </si>
+  <si>
+    <t>EF1</t>
   </si>
 </sst>
 </file>
@@ -736,12 +706,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC9A"/>
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -773,7 +744,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -816,53 +787,110 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1168,7 +1196,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1">
+  <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G51"/>
@@ -1204,997 +1232,992 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:7" s="21" customFormat="1" ht="28.5" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="16" t="s">
+    <row r="2" spans="1:7" s="19" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A2" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="B2" s="21"/>
+      <c r="C2" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="D2" s="22">
+        <v>46042</v>
+      </c>
+      <c r="E2" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="F2" s="23" t="s">
+        <v>48</v>
+      </c>
+      <c r="G2" s="21"/>
+    </row>
+    <row r="3" spans="1:7" s="19" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A3" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" s="15"/>
+      <c r="C3" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="18" t="s">
+      <c r="D3" s="17">
+        <v>46043</v>
+      </c>
+      <c r="E3" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="D2" s="19">
+      <c r="F3" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="G3" s="15"/>
+    </row>
+    <row r="4" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A4" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="B4" s="21"/>
+      <c r="C4" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="D4" s="22">
+        <v>46043</v>
+      </c>
+      <c r="E4" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="F4" s="23" t="s">
+        <v>48</v>
+      </c>
+      <c r="G4" s="21"/>
+    </row>
+    <row r="5" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A5" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="B5" s="21"/>
+      <c r="C5" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="D5" s="22">
+        <v>46044</v>
+      </c>
+      <c r="E5" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="F5" s="23" t="s">
+        <v>65</v>
+      </c>
+      <c r="G5" s="21"/>
+    </row>
+    <row r="6" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A6" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" s="26"/>
+      <c r="C6" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" s="27">
+        <v>46048</v>
+      </c>
+      <c r="E6" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="G6" s="29" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A7" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="15"/>
+      <c r="C7" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" s="17">
         <v>46050</v>
       </c>
-      <c r="E2" s="20" t="s">
+      <c r="E7" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="F7" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="G7" s="15"/>
+    </row>
+    <row r="8" spans="1:7" s="19" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A8" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="B8" s="21"/>
+      <c r="C8" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="D8" s="22">
+        <v>46051</v>
+      </c>
+      <c r="E8" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="F8" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="G8" s="21"/>
+    </row>
+    <row r="9" spans="1:7" s="19" customFormat="1" ht="30" x14ac:dyDescent="0.2">
+      <c r="A9" s="30" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" s="31"/>
+      <c r="C9" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" s="27">
+        <v>46055</v>
+      </c>
+      <c r="E9" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="F9" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="G9" s="32" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A10" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="B10" s="21"/>
+      <c r="C10" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="D10" s="22">
+        <v>46057</v>
+      </c>
+      <c r="E10" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="F10" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="G10" s="21"/>
+    </row>
+    <row r="11" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A11" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="B11" s="21"/>
+      <c r="C11" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="D11" s="22">
+        <v>46064</v>
+      </c>
+      <c r="E11" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="F11" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="G11" s="21"/>
+    </row>
+    <row r="12" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A12" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="B12" s="21"/>
+      <c r="C12" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="D12" s="22">
+        <v>46071</v>
+      </c>
+      <c r="E12" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="F12" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="G12" s="21"/>
+    </row>
+    <row r="13" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A13" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="B13" s="21"/>
+      <c r="C13" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="D13" s="22">
+        <v>46072</v>
+      </c>
+      <c r="E13" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="F13" s="23" t="s">
+        <v>48</v>
+      </c>
+      <c r="G13" s="21"/>
+    </row>
+    <row r="14" spans="1:7" s="19" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A14" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14" s="15"/>
+      <c r="C14" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="D14" s="17">
+        <v>46073</v>
+      </c>
+      <c r="E14" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="F14" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="F2" s="20" t="s">
+      <c r="G14" s="15"/>
+    </row>
+    <row r="15" spans="1:7" s="19" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A15" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="G2" s="17"/>
-    </row>
-    <row r="3" spans="1:7" s="21" customFormat="1" ht="28.5" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="16" t="s">
+      <c r="B15" s="21"/>
+      <c r="C15" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="D15" s="22">
+        <v>46076</v>
+      </c>
+      <c r="E15" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="F15" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="G15" s="21"/>
+    </row>
+    <row r="16" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A16" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="B16" s="15"/>
+      <c r="C16" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="D16" s="22">
+        <v>46076</v>
+      </c>
+      <c r="E16" s="23" t="s">
+        <v>68</v>
+      </c>
+      <c r="F16" s="23" t="s">
+        <v>69</v>
+      </c>
+      <c r="G16" s="15"/>
+    </row>
+    <row r="17" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A17" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="B17" s="21"/>
+      <c r="C17" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="D17" s="22">
+        <v>46078</v>
+      </c>
+      <c r="E17" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="F17" s="23" t="s">
+        <v>58</v>
+      </c>
+      <c r="G17" s="21"/>
+    </row>
+    <row r="18" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A18" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="B18" s="15"/>
+      <c r="C18" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="D18" s="17">
+        <v>46079</v>
+      </c>
+      <c r="E18" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="F18" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="G18" s="15"/>
+    </row>
+    <row r="19" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A19" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="B19" s="21"/>
+      <c r="C19" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="D19" s="22">
+        <v>46079</v>
+      </c>
+      <c r="E19" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="F19" s="23" t="s">
+        <v>62</v>
+      </c>
+      <c r="G19" s="21"/>
+    </row>
+    <row r="20" spans="1:7" s="19" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A20" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="B20" s="21"/>
+      <c r="C20" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="D20" s="22">
+        <v>46080</v>
+      </c>
+      <c r="E20" s="23" t="s">
+        <v>57</v>
+      </c>
+      <c r="F20" s="23" t="s">
+        <v>58</v>
+      </c>
+      <c r="G20" s="21"/>
+    </row>
+    <row r="21" spans="1:7" s="19" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A21" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="B21" s="21"/>
+      <c r="C21" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="D21" s="22">
+        <v>46188</v>
+      </c>
+      <c r="E21" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="F21" s="23" t="s">
+        <v>78</v>
+      </c>
+      <c r="G21" s="21"/>
+    </row>
+    <row r="22" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A22" s="33" t="s">
+        <v>35</v>
+      </c>
+      <c r="B22" s="34"/>
+      <c r="C22" s="33" t="s">
+        <v>36</v>
+      </c>
+      <c r="D22" s="35">
+        <v>46191</v>
+      </c>
+      <c r="E22" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="F22" s="36" t="s">
+        <v>15</v>
+      </c>
+      <c r="G22" s="34">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" s="19" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A23" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="B23" s="21"/>
+      <c r="C23" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="D23" s="22">
+        <v>46192</v>
+      </c>
+      <c r="E23" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="F23" s="23" t="s">
+        <v>78</v>
+      </c>
+      <c r="G23" s="21"/>
+    </row>
+    <row r="24" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A24" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="B24" s="26"/>
+      <c r="C24" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="D24" s="27">
+        <v>46195</v>
+      </c>
+      <c r="E24" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="F24" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="G24" s="29" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A25" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="B25" s="42"/>
+      <c r="C25" s="43" t="s">
         <v>43</v>
       </c>
-      <c r="B3" s="17"/>
-      <c r="C3" s="18" t="s">
+      <c r="D25" s="44">
+        <v>46195</v>
+      </c>
+      <c r="E25" s="45" t="s">
+        <v>49</v>
+      </c>
+      <c r="F25" s="45" t="s">
+        <v>77</v>
+      </c>
+      <c r="G25" s="42"/>
+    </row>
+    <row r="26" spans="1:7" s="19" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A26" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="B26" s="21"/>
+      <c r="C26" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="D26" s="22">
+        <v>46197</v>
+      </c>
+      <c r="E26" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="D3" s="19">
-        <v>46079</v>
-      </c>
-      <c r="E3" s="20" t="s">
-        <v>45</v>
-      </c>
-      <c r="F3" s="20" t="s">
+      <c r="F26" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="G26" s="21"/>
+    </row>
+    <row r="27" spans="1:7" s="19" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A27" s="33" t="s">
+        <v>29</v>
+      </c>
+      <c r="B27" s="34"/>
+      <c r="C27" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="D27" s="35">
+        <v>46198</v>
+      </c>
+      <c r="E27" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="F27" s="36" t="s">
+        <v>8</v>
+      </c>
+      <c r="G27" s="24" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A28" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28" s="15"/>
+      <c r="C28" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="D28" s="17">
+        <v>46206</v>
+      </c>
+      <c r="E28" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="F28" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="G28" s="15" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" s="19" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A29" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="B29" s="21"/>
+      <c r="C29" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="G3" s="17"/>
-    </row>
-    <row r="4" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A4" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="5" t="s">
+      <c r="D29" s="22">
+        <v>46211</v>
+      </c>
+      <c r="E29" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="F29" s="23" t="s">
+        <v>48</v>
+      </c>
+      <c r="G29" s="15" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" s="19" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A30" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="B30" s="21"/>
+      <c r="C30" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="D30" s="22">
+        <v>46212</v>
+      </c>
+      <c r="E30" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="F30" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="G30" s="15" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" s="19" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A31" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="B31" s="21"/>
+      <c r="C31" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="D31" s="22">
+        <v>46213</v>
+      </c>
+      <c r="E31" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="F31" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="G31" s="15" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" s="19" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A32" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="B32" s="21"/>
+      <c r="C32" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="D32" s="22">
+        <v>46216</v>
+      </c>
+      <c r="E32" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="F32" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="G32" s="15" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" s="19" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A33" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="D4" s="7">
-        <v>46191</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="G4" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="30" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="9" t="s">
+      <c r="B33" s="15"/>
+      <c r="C33" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="D33" s="17">
+        <v>46223</v>
+      </c>
+      <c r="E33" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="F33" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="G33" s="15"/>
+    </row>
+    <row r="34" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A34" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="B34" s="15"/>
+      <c r="C34" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="D34" s="17">
+        <v>46224</v>
+      </c>
+      <c r="E34" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="F34" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="G34" s="15"/>
+    </row>
+    <row r="35" spans="1:7" s="19" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A35" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="B35" s="21"/>
+      <c r="C35" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="D35" s="22">
+        <v>46225</v>
+      </c>
+      <c r="E35" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="F35" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="G35" s="21"/>
+    </row>
+    <row r="36" spans="1:7" s="19" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A36" s="43" t="s">
+        <v>59</v>
+      </c>
+      <c r="B36" s="46"/>
+      <c r="C36" s="43" t="s">
+        <v>60</v>
+      </c>
+      <c r="D36" s="47">
+        <v>46226</v>
+      </c>
+      <c r="E36" s="48" t="s">
+        <v>49</v>
+      </c>
+      <c r="F36" s="48" t="s">
+        <v>77</v>
+      </c>
+      <c r="G36" s="46" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A37" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="B37" s="21"/>
+      <c r="C37" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="D37" s="22">
+        <v>46231</v>
+      </c>
+      <c r="E37" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="F37" s="23" t="s">
+        <v>69</v>
+      </c>
+      <c r="G37" s="21"/>
+    </row>
+    <row r="38" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A38" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="B38" s="21"/>
+      <c r="C38" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="D38" s="22">
+        <v>46267</v>
+      </c>
+      <c r="E38" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="F38" s="23" t="s">
+        <v>76</v>
+      </c>
+      <c r="G38" s="21"/>
+    </row>
+    <row r="39" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A39" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="B39" s="38"/>
+      <c r="C39" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="D39" s="39">
+        <v>46272</v>
+      </c>
+      <c r="E39" s="40" t="s">
+        <v>6</v>
+      </c>
+      <c r="F39" s="40" t="s">
+        <v>16</v>
+      </c>
+      <c r="G39" s="38">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" s="19" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A40" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="B40" s="21"/>
+      <c r="C40" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="D40" s="22">
+        <v>46273</v>
+      </c>
+      <c r="E40" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="F40" s="23" t="s">
+        <v>62</v>
+      </c>
+      <c r="G40" s="21"/>
+    </row>
+    <row r="41" spans="1:7" ht="30" x14ac:dyDescent="0.2">
+      <c r="A41" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B41" s="10"/>
+      <c r="C41" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="10"/>
-      <c r="C5" s="11" t="s">
+      <c r="D41" s="12">
+        <v>46274</v>
+      </c>
+      <c r="E41" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="12">
-        <v>46224</v>
-      </c>
-      <c r="E5" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="G5" s="10"/>
-    </row>
-    <row r="6" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A6" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="B6" s="6"/>
-      <c r="C6" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D6" s="7">
-        <v>46195</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="G6" s="6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="30" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="10"/>
-      <c r="C7" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D7" s="12">
-        <v>46288</v>
-      </c>
-      <c r="E7" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="F7" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="G7" s="10"/>
-    </row>
-    <row r="8" spans="1:7" s="21" customFormat="1" ht="14.25" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="B8" s="17"/>
-      <c r="C8" s="22" t="s">
+      <c r="F41" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="G41" s="10">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" s="19" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A42" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="B42" s="21"/>
+      <c r="C42" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="D42" s="22">
+        <v>46275</v>
+      </c>
+      <c r="E42" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="D8" s="19">
-        <v>46043</v>
-      </c>
-      <c r="E8" s="20" t="s">
-        <v>50</v>
-      </c>
-      <c r="F8" s="20" t="s">
-        <v>51</v>
-      </c>
-      <c r="G8" s="17"/>
-    </row>
-    <row r="9" spans="1:7" s="21" customFormat="1" ht="14.25" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="B9" s="17"/>
-      <c r="C9" s="22" t="s">
-        <v>49</v>
-      </c>
-      <c r="D9" s="19">
-        <v>46073</v>
-      </c>
-      <c r="E9" s="20" t="s">
-        <v>50</v>
-      </c>
-      <c r="F9" s="20" t="s">
-        <v>51</v>
-      </c>
-      <c r="G9" s="17"/>
-    </row>
-    <row r="10" spans="1:7" ht="15" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="9" t="s">
+      <c r="F42" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="G42" s="21"/>
+    </row>
+    <row r="43" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A43" s="5" t="s">
         <v>27</v>
-      </c>
-      <c r="B10" s="10"/>
-      <c r="C10" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D10" s="12">
-        <v>46195</v>
-      </c>
-      <c r="E10" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="G10" s="10"/>
-    </row>
-    <row r="11" spans="1:7" ht="15" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="B11" s="10"/>
-      <c r="C11" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D11" s="12">
-        <v>46223</v>
-      </c>
-      <c r="E11" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="F11" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="G11" s="10"/>
-    </row>
-    <row r="12" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A12" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B12" s="6"/>
-      <c r="C12" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D12" s="7">
-        <v>46198</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G12" s="6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A13" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="B13" s="10"/>
-      <c r="C13" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D13" s="12">
-        <v>46272</v>
-      </c>
-      <c r="E13" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="F13" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G13" s="10">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" s="21" customFormat="1" ht="14.25" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="22" t="s">
-        <v>52</v>
-      </c>
-      <c r="B14" s="23"/>
-      <c r="C14" s="22" t="s">
-        <v>53</v>
-      </c>
-      <c r="D14" s="24">
-        <v>46043</v>
-      </c>
-      <c r="E14" s="25" t="s">
-        <v>50</v>
-      </c>
-      <c r="F14" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="G14" s="23"/>
-    </row>
-    <row r="15" spans="1:7" s="21" customFormat="1" ht="14.25" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="22" t="s">
-        <v>52</v>
-      </c>
-      <c r="B15" s="23"/>
-      <c r="C15" s="22" t="s">
-        <v>53</v>
-      </c>
-      <c r="D15" s="24">
-        <v>46076</v>
-      </c>
-      <c r="E15" s="25" t="s">
-        <v>55</v>
-      </c>
-      <c r="F15" s="25" t="s">
-        <v>56</v>
-      </c>
-      <c r="G15" s="23"/>
-    </row>
-    <row r="16" spans="1:7" ht="15" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="B16" s="6"/>
-      <c r="C16" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D16" s="7">
-        <v>46188</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="F16" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G16" s="6"/>
-    </row>
-    <row r="17" spans="1:7" ht="30" x14ac:dyDescent="0.2">
-      <c r="A17" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="B17" s="10"/>
-      <c r="C17" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D17" s="12">
-        <v>46274</v>
-      </c>
-      <c r="E17" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="F17" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="G17" s="10">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="15" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="B18" s="6"/>
-      <c r="C18" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D18" s="7">
-        <v>46225</v>
-      </c>
-      <c r="E18" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="F18" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="G18" s="6"/>
-    </row>
-    <row r="19" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A19" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="B19" s="6"/>
-      <c r="C19" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D19" s="7">
-        <v>46276</v>
-      </c>
-      <c r="E19" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F19" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="G19" s="6">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" s="21" customFormat="1" ht="14.25" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="22" t="s">
-        <v>57</v>
-      </c>
-      <c r="B20" s="23"/>
-      <c r="C20" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="D20" s="24">
-        <v>46042</v>
-      </c>
-      <c r="E20" s="25" t="s">
-        <v>55</v>
-      </c>
-      <c r="F20" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="G20" s="23"/>
-    </row>
-    <row r="21" spans="1:7" s="21" customFormat="1" ht="14.25" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="22" t="s">
-        <v>57</v>
-      </c>
-      <c r="B21" s="23"/>
-      <c r="C21" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="D21" s="24">
-        <v>46071</v>
-      </c>
-      <c r="E21" s="25" t="s">
-        <v>55</v>
-      </c>
-      <c r="F21" s="25" t="s">
-        <v>59</v>
-      </c>
-      <c r="G21" s="23"/>
-    </row>
-    <row r="22" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A22" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="B22" s="10"/>
-      <c r="C22" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D22" s="12">
-        <v>46287</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="F22" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="G22" s="10">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A23" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="B23" s="6"/>
-      <c r="C23" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D23" s="7">
-        <v>46288</v>
-      </c>
-      <c r="E23" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="F23" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="G23" s="6">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="15" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="B24" s="6"/>
-      <c r="C24" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D24" s="7">
-        <v>46273</v>
-      </c>
-      <c r="E24" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F24" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="G24" s="6"/>
-    </row>
-    <row r="25" spans="1:7" ht="15" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="B25" s="6"/>
-      <c r="C25" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D25" s="7">
-        <v>46286</v>
-      </c>
-      <c r="E25" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F25" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="G25" s="6"/>
-    </row>
-    <row r="26" spans="1:7" s="21" customFormat="1" ht="14.25" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="B26" s="23"/>
-      <c r="C26" s="22" t="s">
-        <v>61</v>
-      </c>
-      <c r="D26" s="24">
-        <v>46057</v>
-      </c>
-      <c r="E26" s="25" t="s">
-        <v>55</v>
-      </c>
-      <c r="F26" s="25" t="s">
-        <v>62</v>
-      </c>
-      <c r="G26" s="23"/>
-    </row>
-    <row r="27" spans="1:7" s="21" customFormat="1" ht="14.25" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="B27" s="23"/>
-      <c r="C27" s="22" t="s">
-        <v>61</v>
-      </c>
-      <c r="D27" s="24">
-        <v>46080</v>
-      </c>
-      <c r="E27" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="F27" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="G27" s="23"/>
-    </row>
-    <row r="28" spans="1:7" ht="15" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="B28" s="6"/>
-      <c r="C28" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D28" s="7">
-        <v>46192</v>
-      </c>
-      <c r="E28" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F28" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G28" s="6"/>
-    </row>
-    <row r="29" spans="1:7" ht="30" x14ac:dyDescent="0.2">
-      <c r="A29" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="B29" s="10"/>
-      <c r="C29" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="D29" s="14">
-        <v>46055</v>
-      </c>
-      <c r="E29" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="F29" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="G29" s="26" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A30" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B30" s="6"/>
-      <c r="C30" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D30" s="7">
-        <v>46048</v>
-      </c>
-      <c r="E30" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F30" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="G30" s="27" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="15" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="B31" s="6"/>
-      <c r="C31" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D31" s="7">
-        <v>46290</v>
-      </c>
-      <c r="E31" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F31" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="G31" s="6"/>
-    </row>
-    <row r="32" spans="1:7" s="21" customFormat="1" ht="14.25" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="22" t="s">
-        <v>65</v>
-      </c>
-      <c r="B32" s="23"/>
-      <c r="C32" s="22" t="s">
-        <v>66</v>
-      </c>
-      <c r="D32" s="24">
-        <v>46051</v>
-      </c>
-      <c r="E32" s="25" t="s">
-        <v>55</v>
-      </c>
-      <c r="F32" s="25" t="s">
-        <v>67</v>
-      </c>
-      <c r="G32" s="23"/>
-    </row>
-    <row r="33" spans="1:7" s="21" customFormat="1" ht="14.25" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="22" t="s">
-        <v>65</v>
-      </c>
-      <c r="B33" s="23"/>
-      <c r="C33" s="22" t="s">
-        <v>66</v>
-      </c>
-      <c r="D33" s="24">
-        <v>46079</v>
-      </c>
-      <c r="E33" s="25" t="s">
-        <v>55</v>
-      </c>
-      <c r="F33" s="25" t="s">
-        <v>68</v>
-      </c>
-      <c r="G33" s="23"/>
-    </row>
-    <row r="34" spans="1:7" ht="30" x14ac:dyDescent="0.2">
-      <c r="A34" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="B34" s="10"/>
-      <c r="C34" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D34" s="12">
-        <v>46206</v>
-      </c>
-      <c r="E34" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="F34" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="G34" s="28" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A35" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="B35" s="6"/>
-      <c r="C35" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D35" s="7">
-        <v>46211</v>
-      </c>
-      <c r="E35" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="F35" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G35" s="28" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" ht="15" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B36" s="6"/>
-      <c r="C36" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D36" s="7">
-        <v>46275</v>
-      </c>
-      <c r="E36" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F36" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="G36" s="6"/>
-    </row>
-    <row r="37" spans="1:7" ht="15" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B37" s="6"/>
-      <c r="C37" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D37" s="7">
-        <v>46290</v>
-      </c>
-      <c r="E37" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F37" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="G37" s="6"/>
-    </row>
-    <row r="38" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A38" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="B38" s="6"/>
-      <c r="C38" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D38" s="7">
-        <v>46212</v>
-      </c>
-      <c r="E38" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F38" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="G38" s="28" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" ht="15" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B39" s="6"/>
-      <c r="C39" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D39" s="7">
-        <v>46072</v>
-      </c>
-      <c r="E39" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F39" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G39" s="6"/>
-    </row>
-    <row r="40" spans="1:7" ht="15" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B40" s="6"/>
-      <c r="C40" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D40" s="7">
-        <v>46197</v>
-      </c>
-      <c r="E40" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="F40" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="G40" s="6"/>
-    </row>
-    <row r="41" spans="1:7" ht="15" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B41" s="6"/>
-      <c r="C41" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D41" s="7">
-        <v>46231</v>
-      </c>
-      <c r="E41" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F41" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="G41" s="6"/>
-    </row>
-    <row r="42" spans="1:7" ht="15" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B42" s="6"/>
-      <c r="C42" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D42" s="7">
-        <v>46267</v>
-      </c>
-      <c r="E42" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F42" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="G42" s="6"/>
-    </row>
-    <row r="43" spans="1:7" ht="15" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="5" t="s">
-        <v>37</v>
       </c>
       <c r="B43" s="6"/>
       <c r="C43" s="5" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="D43" s="7">
-        <v>46287</v>
+        <v>46276</v>
       </c>
       <c r="E43" s="8" t="s">
         <v>9</v>
       </c>
       <c r="F43" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="G43" s="6"/>
-    </row>
-    <row r="44" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A44" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="B44" s="6"/>
-      <c r="C44" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D44" s="7">
-        <v>46216</v>
-      </c>
-      <c r="E44" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G43" s="6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" s="19" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A44" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="B44" s="21"/>
+      <c r="C44" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="D44" s="22">
+        <v>46286</v>
+      </c>
+      <c r="E44" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="F44" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="G44" s="21"/>
+    </row>
+    <row r="45" spans="1:7" s="19" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A45" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B45" s="10"/>
+      <c r="C45" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D45" s="12">
+        <v>46287</v>
+      </c>
+      <c r="E45" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="F45" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="G45" s="10">
         <v>9</v>
       </c>
-      <c r="F44" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="G44" s="28" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" s="21" customFormat="1" ht="28.5" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="B45" s="17"/>
-      <c r="C45" s="22" t="s">
-        <v>73</v>
-      </c>
-      <c r="D45" s="24">
-        <v>46076</v>
-      </c>
-      <c r="E45" s="25" t="s">
+    </row>
+    <row r="46" spans="1:7" s="19" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A46" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="F45" s="25" t="s">
+      <c r="B46" s="21"/>
+      <c r="C46" s="20" t="s">
         <v>75</v>
       </c>
-      <c r="G45" s="17"/>
-    </row>
-    <row r="46" spans="1:7" s="21" customFormat="1" ht="14.25" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="B46" s="23"/>
-      <c r="C46" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="D46" s="24">
-        <v>46044</v>
-      </c>
-      <c r="E46" s="25" t="s">
-        <v>50</v>
-      </c>
-      <c r="F46" s="25" t="s">
-        <v>71</v>
-      </c>
-      <c r="G46" s="23"/>
-    </row>
-    <row r="47" spans="1:7" s="21" customFormat="1" ht="14.25" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="B47" s="23"/>
-      <c r="C47" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="D47" s="24">
-        <v>46064</v>
-      </c>
-      <c r="E47" s="25" t="s">
-        <v>50</v>
-      </c>
-      <c r="F47" s="25" t="s">
-        <v>62</v>
-      </c>
-      <c r="G47" s="23"/>
-    </row>
-    <row r="48" spans="1:7" s="21" customFormat="1" ht="14.25" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="B48" s="23"/>
-      <c r="C48" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="D48" s="24">
-        <v>46078</v>
-      </c>
-      <c r="E48" s="25" t="s">
-        <v>50</v>
-      </c>
-      <c r="F48" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="G48" s="23"/>
+      <c r="D46" s="22">
+        <v>46287</v>
+      </c>
+      <c r="E46" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="F46" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="G46" s="21"/>
+    </row>
+    <row r="47" spans="1:7" s="19" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A47" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B47" s="6"/>
+      <c r="C47" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D47" s="7">
+        <v>46287</v>
+      </c>
+      <c r="E47" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="F47" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G47" s="6"/>
+    </row>
+    <row r="48" spans="1:7" s="19" customFormat="1" ht="30" x14ac:dyDescent="0.2">
+      <c r="A48" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B48" s="10"/>
+      <c r="C48" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D48" s="12">
+        <v>46288</v>
+      </c>
+      <c r="E48" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="F48" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="G48" s="10"/>
     </row>
     <row r="49" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A49" s="5" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="B49" s="6"/>
       <c r="C49" s="5" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="D49" s="7">
-        <v>46213</v>
+        <v>46288</v>
       </c>
       <c r="E49" s="8" t="s">
         <v>6</v>
       </c>
       <c r="F49" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="G49" s="28" t="s">
-        <v>76</v>
+        <v>10</v>
+      </c>
+      <c r="G49" s="6">
+        <v>9</v>
       </c>
     </row>
     <row r="50" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A50" s="5" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="B50" s="6"/>
       <c r="C50" s="5" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="D50" s="7">
-        <v>46226</v>
+        <v>46290</v>
       </c>
       <c r="E50" s="8" t="s">
         <v>9</v>
       </c>
       <c r="F50" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="G50" s="29" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" ht="15" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B51" s="6"/>
-      <c r="C51" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="D51" s="7">
-        <v>46287</v>
-      </c>
-      <c r="E51" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="F51" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="G51" s="6"/>
+        <v>15</v>
+      </c>
+      <c r="G50" s="6"/>
+    </row>
+    <row r="51" spans="1:7" s="19" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A51" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="B51" s="21"/>
+      <c r="C51" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="D51" s="22">
+        <v>46290</v>
+      </c>
+      <c r="E51" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="F51" s="23" t="s">
+        <v>76</v>
+      </c>
+      <c r="G51" s="21"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:G51" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="6">
-      <customFilters>
-        <customFilter operator="notEqual" val=" "/>
-      </customFilters>
-    </filterColumn>
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:G50">
-      <sortCondition ref="G1:G51"/>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G51">
+      <sortCondition ref="D1:D51"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
